--- a/filter_instock_2VRDS.xlsx
+++ b/filter_instock_2VRDS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,6 +468,42 @@
         <is>
           <t>입고수량</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1785369496672</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>4B/L</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>F7701</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H2" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock_2VRDS.xlsx
+++ b/filter_instock_2VRDS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,36 @@
       </c>
       <c r="H2" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1785369509005</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>가스켓</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4B/L</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>F7701</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
